--- a/stdharvest/samples/sample_download.xlsx
+++ b/stdharvest/samples/sample_download.xlsx
@@ -1,56 +1,172 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6e16e05619048d6/ドキュメント/new_3gpp_and_ieee/get_3gpp_and_ieee_v3_202604/stdharvest/samples/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_3015AAAF869BFE086F05BD24D9A7D17E533EE0D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB6320E-71D8-4631-B1A6-D7A78E1DAD13}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t>SourceType</t>
+  </si>
+  <si>
+    <t>ieee</t>
+  </si>
+  <si>
+    <t>OutputRootFolder</t>
+  </si>
+  <si>
+    <t>JobName</t>
+  </si>
+  <si>
+    <t>ieee_sample_job</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>SavedPath</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>LastRunAt</t>
+  </si>
+  <si>
+    <t>11-26-0819-00-00bq Multiple BSSID set in IMMW</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>C:\Users\yohei\Downloads\std_docs1\20260425_ieee_sample_job\raw\001_11-26-0819-00-00bq Multiple BSSID set in IMMW\11-26-0819-00-00bq-multiple-bssid-set-in-immw.pptx</t>
+  </si>
+  <si>
+    <t>downloaded, pdf 1, html 1</t>
+  </si>
+  <si>
+    <t>2026-04-25 00:25:41</t>
+  </si>
+  <si>
+    <t>ProxyURL</t>
+  </si>
+  <si>
+    <t>TimeoutSec</t>
+  </si>
+  <si>
+    <t>RetryCount</t>
+  </si>
+  <si>
+    <t>SleepSec</t>
+  </si>
+  <si>
+    <t>OverwriteExisting</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>MinFileSizeKB</t>
+  </si>
+  <si>
+    <t>MaxFileSizeMB</t>
+  </si>
+  <si>
+    <t>OnTooSmallFile</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>OnTooLargeFile</t>
+  </si>
+  <si>
+    <t>skip</t>
+  </si>
+  <si>
+    <t>KillOfficeAppsBeforeRun</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>DownloadWorkers</t>
+  </si>
+  <si>
+    <t>UnzipWorkers</t>
+  </si>
+  <si>
+    <t>PdfWorkers</t>
+  </si>
+  <si>
+    <t>HtmlWorkers</t>
+  </si>
+  <si>
+    <t>CombineHtmlBatchSize</t>
+  </si>
+  <si>
+    <t>C:\Users\yohei\Downloads\std_docs1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
-      <family val="3"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
     </font>
     <font>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -81,85 +197,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -447,304 +504,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SourceType</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ieee</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>OutputRootFolder</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C:\Users\yohei\Downloads\std_docs1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>JobName</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ieee_sample_job</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>SavedPath</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>LastRunAt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>11-26-0819-00-00bq Multiple BSSID set in IMMW</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>C:\Users\yohei\Downloads\std_docs1\20260425_ieee_sample_job\raw\001_11-26-0819-00-00bq Multiple BSSID set in IMMW\11-26-0819-00-00bq-multiple-bssid-set-in-immw.pptx</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>downloaded, pdf 1, html 1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-04-25 00:25:41</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <dataValidations count="1">
-    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="SourceType" error="3gpp か ieee を選択してください" type="list">
+    <dataValidation type="list" errorTitle="SourceType" error="3gpp か ieee を選択してください" sqref="B1" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"3gpp,ieee"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ProxyURL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>TimeoutSec</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
         <v>60</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>RetryCount</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>SleepSec</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>OverwriteExisting</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>MinFileSizeKB</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>10</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>MaxFileSizeMB</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>100</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>OnTooSmallFile</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>OnTooLargeFile</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>skip</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>KillOfficeAppsBeforeRun</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>DownloadWorkers</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11">
         <v>8</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>UnzipWorkers</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12">
         <v>4</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>PdfWorkers</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13">
         <v>2</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>HtmlWorkers</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14">
         <v>6</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>CombineHtmlBatchSize</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <dataValidations count="3">
-    <dataValidation sqref="B5 B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="B5 B10" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="B8" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"error,skip"</formula1>
     </dataValidation>
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="B9" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"skip,pdf_only,keep_raw"</formula1>
     </dataValidation>
   </dataValidations>

--- a/stdharvest/samples/sample_download.xlsx
+++ b/stdharvest/samples/sample_download.xlsx
@@ -1,172 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6e16e05619048d6/ドキュメント/new_3gpp_and_ieee/get_3gpp_and_ieee_v3_202604/stdharvest/samples/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_3015AAAF869BFE086F05BD24D9A7D17E533EE0D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB6320E-71D8-4631-B1A6-D7A78E1DAD13}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
-  <si>
-    <t>SourceType</t>
-  </si>
-  <si>
-    <t>ieee</t>
-  </si>
-  <si>
-    <t>OutputRootFolder</t>
-  </si>
-  <si>
-    <t>JobName</t>
-  </si>
-  <si>
-    <t>ieee_sample_job</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>SavedPath</t>
-  </si>
-  <si>
-    <t>Message</t>
-  </si>
-  <si>
-    <t>LastRunAt</t>
-  </si>
-  <si>
-    <t>11-26-0819-00-00bq Multiple BSSID set in IMMW</t>
-  </si>
-  <si>
-    <t>DONE</t>
-  </si>
-  <si>
-    <t>C:\Users\yohei\Downloads\std_docs1\20260425_ieee_sample_job\raw\001_11-26-0819-00-00bq Multiple BSSID set in IMMW\11-26-0819-00-00bq-multiple-bssid-set-in-immw.pptx</t>
-  </si>
-  <si>
-    <t>downloaded, pdf 1, html 1</t>
-  </si>
-  <si>
-    <t>2026-04-25 00:25:41</t>
-  </si>
-  <si>
-    <t>ProxyURL</t>
-  </si>
-  <si>
-    <t>TimeoutSec</t>
-  </si>
-  <si>
-    <t>RetryCount</t>
-  </si>
-  <si>
-    <t>SleepSec</t>
-  </si>
-  <si>
-    <t>OverwriteExisting</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>MinFileSizeKB</t>
-  </si>
-  <si>
-    <t>MaxFileSizeMB</t>
-  </si>
-  <si>
-    <t>OnTooSmallFile</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>OnTooLargeFile</t>
-  </si>
-  <si>
-    <t>skip</t>
-  </si>
-  <si>
-    <t>KillOfficeAppsBeforeRun</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>DownloadWorkers</t>
-  </si>
-  <si>
-    <t>UnzipWorkers</t>
-  </si>
-  <si>
-    <t>PdfWorkers</t>
-  </si>
-  <si>
-    <t>HtmlWorkers</t>
-  </si>
-  <si>
-    <t>CombineHtmlBatchSize</t>
-  </si>
-  <si>
-    <t>C:\Users\yohei\Downloads\std_docs1</t>
-    <phoneticPr fontId="3"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0563C1"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
       <family val="3"/>
-      <charset val="128"/>
+      <sz val="6"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -197,26 +80,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -504,228 +448,612 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SourceType</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ieee</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>OutputRootFolder</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>JobName</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ieee_sample_job</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>SavedPath</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>LastRunAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\001_Download\11-24-1918-02-00bn-hip-edca-sp2-tbd-resolution.pptx</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\002_Download\11-24-2007-06-00bn-pdt-mac-p-edca.docx</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\003_Download\11-24-2007-05-00bn-pdt-mac-p-edca.docx</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\004_Download\11-24-2007-04-00bn-pdt-mac-p-edca.docx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\005_Download\11-24-1918-01-00bn-hip-edca-sp2-tbd-resolution.pptx</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\006_Download\11-24-1706-02-00bn-multi-user-edca-parameter-management-in-npca-operation.pptx</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\007_Download\11-24-1706-01-00bn-multi-user-edca-parameter-management-in-npca-operation.pptx</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\008_Download\11-24-2007-03-00bn-pdt-mac-p-edca.docx</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\009_Download\11-24-2007-02-00bn-pdt-mac-p-edca.docx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\010_Download\11-24-2007-01-00bn-pdt-mac-p-edca.docx</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\011_Download\11-24-2007-00-00bn-pdt-mac-p-edca.docx</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\012_Download\11-24-1967-01-00bn-pdt-hip-edca.docx</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>downloaded, pdf 1, html 1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-04-25 22:07:50</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorTitle="SourceType" error="3gpp か ieee を選択してください" sqref="B1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="SourceType" error="3gpp か ieee を選択してください" type="list">
       <formula1>"3gpp,ieee"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="https://mentor.ieee.org/802.11/dcn/24/11-24-1918-02-00bn-hip-edca-sp2-tbd-resolution.pptx" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" display="https://mentor.ieee.org/802.11/dcn/24/11-24-2007-06-00bn-pdt-mac-p-edca.docx" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="https://mentor.ieee.org/802.11/dcn/24/11-24-2007-05-00bn-pdt-mac-p-edca.docx" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" display="https://mentor.ieee.org/802.11/dcn/24/11-24-2007-04-00bn-pdt-mac-p-edca.docx" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" display="https://mentor.ieee.org/802.11/dcn/24/11-24-1918-01-00bn-hip-edca-sp2-tbd-resolution.pptx" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" display="https://mentor.ieee.org/802.11/dcn/24/11-24-1706-02-00bn-multi-user-edca-parameter-management-in-npca-operation.pptx" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" display="https://mentor.ieee.org/802.11/dcn/24/11-24-1706-01-00bn-multi-user-edca-parameter-management-in-npca-operation.pptx" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="https://mentor.ieee.org/802.11/dcn/24/11-24-2007-03-00bn-pdt-mac-p-edca.docx" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" display="https://mentor.ieee.org/802.11/dcn/24/11-24-2007-02-00bn-pdt-mac-p-edca.docx" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" display="https://mentor.ieee.org/802.11/dcn/24/11-24-2007-01-00bn-pdt-mac-p-edca.docx" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" display="https://mentor.ieee.org/802.11/dcn/24/11-24-2007-00-00bn-pdt-mac-p-edca.docx" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" display="https://mentor.ieee.org/802.11/dcn/24/11-24-1967-01-00bn-pdt-hip-edca.docx" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ProxyURL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>TimeoutSec</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>RetryCount</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SleepSec</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>OverwriteExisting</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MinFileSizeKB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MaxFileSizeMB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OnTooSmallFile</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OnTooLargeFile</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>KillOfficeAppsBeforeRun</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>DownloadWorkers</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>UnzipWorkers</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>PdfWorkers</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>HtmlWorkers</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CombineHtmlBatchSize</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="B5 B10" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation sqref="B5 B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B8" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"error,skip"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B9" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"skip,pdf_only,keep_raw"</formula1>
     </dataValidation>
   </dataValidations>

--- a/stdharvest/samples/sample_download.xlsx
+++ b/stdharvest/samples/sample_download.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -36,13 +36,6 @@
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
       <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="2"/>
       <sz val="6"/>
       <scheme val="minor"/>
     </font>
@@ -484,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3</t>
         </is>
       </c>
     </row>
@@ -542,7 +535,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\001_Download\11-24-1918-02-00bn-hip-edca-sp2-tbd-resolution.pptx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\001_Download\11-24-1918-02-00bn-hip-edca-sp2-tbd-resolution.pptx</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -552,7 +545,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -569,7 +562,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\002_Download\11-24-2007-06-00bn-pdt-mac-p-edca.docx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\002_Download\11-24-2007-06-00bn-pdt-mac-p-edca.docx</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -579,7 +572,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -596,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\003_Download\11-24-2007-05-00bn-pdt-mac-p-edca.docx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\003_Download\11-24-2007-05-00bn-pdt-mac-p-edca.docx</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -606,7 +599,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -623,7 +616,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\004_Download\11-24-2007-04-00bn-pdt-mac-p-edca.docx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\004_Download\11-24-2007-04-00bn-pdt-mac-p-edca.docx</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -633,7 +626,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -650,7 +643,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\005_Download\11-24-1918-01-00bn-hip-edca-sp2-tbd-resolution.pptx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\005_Download\11-24-1918-01-00bn-hip-edca-sp2-tbd-resolution.pptx</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -660,7 +653,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -677,7 +670,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\006_Download\11-24-1706-02-00bn-multi-user-edca-parameter-management-in-npca-operation.pptx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\006_Download\11-24-1706-02-00bn-multi-user-edca-parameter-management-in-npca-operation.pptx</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -687,7 +680,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -704,7 +697,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\007_Download\11-24-1706-01-00bn-multi-user-edca-parameter-management-in-npca-operation.pptx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\007_Download\11-24-1706-01-00bn-multi-user-edca-parameter-management-in-npca-operation.pptx</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -714,7 +707,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -731,7 +724,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\008_Download\11-24-2007-03-00bn-pdt-mac-p-edca.docx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\008_Download\11-24-2007-03-00bn-pdt-mac-p-edca.docx</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -741,7 +734,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -758,7 +751,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\009_Download\11-24-2007-02-00bn-pdt-mac-p-edca.docx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\009_Download\11-24-2007-02-00bn-pdt-mac-p-edca.docx</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -768,7 +761,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -785,7 +778,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\010_Download\11-24-2007-01-00bn-pdt-mac-p-edca.docx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\010_Download\11-24-2007-01-00bn-pdt-mac-p-edca.docx</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -795,7 +788,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -812,7 +805,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\011_Download\11-24-2007-00-00bn-pdt-mac-p-edca.docx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\011_Download\11-24-2007-00-00bn-pdt-mac-p-edca.docx</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -822,7 +815,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
@@ -839,7 +832,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C:\Users\yohei\Downloads\std_doc_2\20260425_ieee_sample_job\raw\012_Download\11-24-1967-01-00bn-pdt-hip-edca.docx</t>
+          <t>C:\Users\yohei\Downloads\std_doc_3\20260501_ieee_sample_job\raw\012_Download\11-24-1967-01-00bn-pdt-hip-edca.docx</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -849,7 +842,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-25 22:07:50</t>
+          <t>2026-05-01 03:29:38</t>
         </is>
       </c>
     </row>
